--- a/seo-geo/tracking/issue-tracker.xlsx
+++ b/seo-geo/tracking/issue-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Issues" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Issues'!$A$1:$J$240</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Issues'!$A$1:$J$249</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,14 +439,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J240"/>
+  <dimension ref="A1:J249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
     <col width="80" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
@@ -11978,10 +11978,442 @@
       </c>
       <c r="J240" s="2" t="inlineStr"/>
     </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>AS-240</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>New since 2026-09-03</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>New page: Brand Store Design</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/brand-store-design/</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>New page found live, not in the original audit: thin content, no meta description, no alt text</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/brand-store-design/ did not exist on 2026-09-03 (confirmed absent from the page sitemap that day) and is live as of the 2026-09-07 re-check: HTTP 200, in the page sitemap, published page count rose from 50 to 51. It has one H1 ("Brand Store Design"), 17 words of body copy, no meta description, and 48 of 48 images with empty alt text. It carries the same sitewide Organization/ProfessionalService schema as every other page (see the schema rows above), so it inherits that issue too.</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>Give this page the same treatment as the other primary pages: write a meta description, expand the body copy well past 17 words (what Brand Store design work includes, examples, a link to the portfolio gallery), and add alt text to all 48 images.</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>AS-241</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>New since 2026-09-03</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>New page: Brand Store Design</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/brand-store-design/</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>No call to action visible in the first mobile screen</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>Rendered at 390x844, the only CTA ("Contact") is inside the collapsed nav menu, same pattern as most other pages.</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>Add a visible CTA button under the H1.</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>AS-242</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>New since 2026-09-03: dsm-attachment-category archives</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>DSM attachment category archive: ABG</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/blog/dsm-attachment-category/abg/</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>New junk taxonomy archive found live and indexable, not present on 2026-09-03</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/blog/dsm-attachment-category/abg/ did not exist on 2026-09-03. As of 2026-09-07 it returns HTTP 200, self canonical, no noindex meta tag, and is listed in a new child sitemap at https://www.albertscott.com/dsm-attachment-category-sitemap.xml (7 URLs total, all named after client brands: ABG, BeYoutifull, Katjes, Magmod, Mouthwatchers, Rufus, Tabanero). This is the same pattern as the project_category archives already flagged: an auto-generated taxonomy archive with no unique content, here from a Divi Supreme Modules plugin feature.</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>In All in One SEO &gt; Search Appearance &gt; Taxonomies, find "DSM Attachment Category" (or the equivalent label the Divi Supreme Modules plugin registers) and set "Show in search results" to No and untick "Include in sitemap", the same fix already applied to the other taxonomy archives.</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>AS-243</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>New since 2026-09-03: dsm-attachment-category archives</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>DSM attachment category archive: BeYoutifull</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/blog/dsm-attachment-category/beyoutifull/</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>New junk taxonomy archive found live and indexable, not present on 2026-09-03</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/blog/dsm-attachment-category/beyoutifull/ did not exist on 2026-09-03. As of 2026-09-07 it returns HTTP 200, self canonical, no noindex meta tag, and is listed in a new child sitemap at https://www.albertscott.com/dsm-attachment-category-sitemap.xml (7 URLs total, all named after client brands: ABG, BeYoutifull, Katjes, Magmod, Mouthwatchers, Rufus, Tabanero). This is the same pattern as the project_category archives already flagged: an auto-generated taxonomy archive with no unique content, here from a Divi Supreme Modules plugin feature.</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>In All in One SEO &gt; Search Appearance &gt; Taxonomies, find "DSM Attachment Category" (or the equivalent label the Divi Supreme Modules plugin registers) and set "Show in search results" to No and untick "Include in sitemap", the same fix already applied to the other taxonomy archives.</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>AS-244</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>New since 2026-09-03: dsm-attachment-category archives</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>DSM attachment category archive: Katjes</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/blog/dsm-attachment-category/katjes/</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>New junk taxonomy archive found live and indexable, not present on 2026-09-03</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/blog/dsm-attachment-category/katjes/ did not exist on 2026-09-03. As of 2026-09-07 it returns HTTP 200, self canonical, no noindex meta tag, and is listed in a new child sitemap at https://www.albertscott.com/dsm-attachment-category-sitemap.xml (7 URLs total, all named after client brands: ABG, BeYoutifull, Katjes, Magmod, Mouthwatchers, Rufus, Tabanero). This is the same pattern as the project_category archives already flagged: an auto-generated taxonomy archive with no unique content, here from a Divi Supreme Modules plugin feature.</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>In All in One SEO &gt; Search Appearance &gt; Taxonomies, find "DSM Attachment Category" (or the equivalent label the Divi Supreme Modules plugin registers) and set "Show in search results" to No and untick "Include in sitemap", the same fix already applied to the other taxonomy archives.</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>AS-245</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>New since 2026-09-03: dsm-attachment-category archives</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>DSM attachment category archive: Magmod</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/blog/dsm-attachment-category/magmod/</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>New junk taxonomy archive found live and indexable, not present on 2026-09-03</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/blog/dsm-attachment-category/magmod/ did not exist on 2026-09-03. As of 2026-09-07 it returns HTTP 200, self canonical, no noindex meta tag, and is listed in a new child sitemap at https://www.albertscott.com/dsm-attachment-category-sitemap.xml (7 URLs total, all named after client brands: ABG, BeYoutifull, Katjes, Magmod, Mouthwatchers, Rufus, Tabanero). This is the same pattern as the project_category archives already flagged: an auto-generated taxonomy archive with no unique content, here from a Divi Supreme Modules plugin feature.</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>In All in One SEO &gt; Search Appearance &gt; Taxonomies, find "DSM Attachment Category" (or the equivalent label the Divi Supreme Modules plugin registers) and set "Show in search results" to No and untick "Include in sitemap", the same fix already applied to the other taxonomy archives.</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>AS-246</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>New since 2026-09-03: dsm-attachment-category archives</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>DSM attachment category archive: Mouthwatchers</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/blog/dsm-attachment-category/mouthwatchers/</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>New junk taxonomy archive found live and indexable, not present on 2026-09-03</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/blog/dsm-attachment-category/mouthwatchers/ did not exist on 2026-09-03. As of 2026-09-07 it returns HTTP 200, self canonical, no noindex meta tag, and is listed in a new child sitemap at https://www.albertscott.com/dsm-attachment-category-sitemap.xml (7 URLs total, all named after client brands: ABG, BeYoutifull, Katjes, Magmod, Mouthwatchers, Rufus, Tabanero). This is the same pattern as the project_category archives already flagged: an auto-generated taxonomy archive with no unique content, here from a Divi Supreme Modules plugin feature.</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>In All in One SEO &gt; Search Appearance &gt; Taxonomies, find "DSM Attachment Category" (or the equivalent label the Divi Supreme Modules plugin registers) and set "Show in search results" to No and untick "Include in sitemap", the same fix already applied to the other taxonomy archives.</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>AS-247</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>New since 2026-09-03: dsm-attachment-category archives</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>DSM attachment category archive: Rufus</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/blog/dsm-attachment-category/rufus/</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>New junk taxonomy archive found live and indexable, not present on 2026-09-03</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/blog/dsm-attachment-category/rufus/ did not exist on 2026-09-03. As of 2026-09-07 it returns HTTP 200, self canonical, no noindex meta tag, and is listed in a new child sitemap at https://www.albertscott.com/dsm-attachment-category-sitemap.xml (7 URLs total, all named after client brands: ABG, BeYoutifull, Katjes, Magmod, Mouthwatchers, Rufus, Tabanero). This is the same pattern as the project_category archives already flagged: an auto-generated taxonomy archive with no unique content, here from a Divi Supreme Modules plugin feature.</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>In All in One SEO &gt; Search Appearance &gt; Taxonomies, find "DSM Attachment Category" (or the equivalent label the Divi Supreme Modules plugin registers) and set "Show in search results" to No and untick "Include in sitemap", the same fix already applied to the other taxonomy archives.</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>AS-248</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>New since 2026-09-03: dsm-attachment-category archives</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>DSM attachment category archive: Tabanero</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/blog/dsm-attachment-category/tabanero/</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>New junk taxonomy archive found live and indexable, not present on 2026-09-03</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/blog/dsm-attachment-category/tabanero/ did not exist on 2026-09-03. As of 2026-09-07 it returns HTTP 200, self canonical, no noindex meta tag, and is listed in a new child sitemap at https://www.albertscott.com/dsm-attachment-category-sitemap.xml (7 URLs total, all named after client brands: ABG, BeYoutifull, Katjes, Magmod, Mouthwatchers, Rufus, Tabanero). This is the same pattern as the project_category archives already flagged: an auto-generated taxonomy archive with no unique content, here from a Divi Supreme Modules plugin feature.</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>In All in One SEO &gt; Search Appearance &gt; Taxonomies, find "DSM Attachment Category" (or the equivalent label the Divi Supreme Modules plugin registers) and set "Show in search results" to No and untick "Include in sitemap", the same fix already applied to the other taxonomy archives.</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J240"/>
+  <autoFilter ref="A1:J249"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J240" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J249" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Skipped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12225,6 +12657,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId237"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId248"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seo-geo/tracking/issue-tracker.xlsx
+++ b/seo-geo/tracking/issue-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Issues" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Issues'!$A$1:$J$250</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Issues'!$A$1:$J$252</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J250"/>
+  <dimension ref="A1:J252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -475,7 +475,7 @@
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -578,7 +578,7 @@
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Open, urgent</t>
+          <t>Open, urgent (confirmed again 2026-09-14: article still not restored, 5 days after it was found deleted)</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -964,7 +968,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1012,7 +1020,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1060,7 +1072,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1108,7 +1124,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1156,7 +1176,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1204,7 +1228,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1252,7 +1280,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1300,7 +1332,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1348,7 +1384,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1396,7 +1436,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1444,7 +1488,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1492,7 +1540,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1540,7 +1592,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1588,7 +1644,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1636,7 +1696,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1684,7 +1748,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1732,7 +1800,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1780,7 +1852,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1876,7 +1952,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1924,7 +2004,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1972,7 +2056,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2020,7 +2108,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2116,7 +2208,11 @@
           <t>R5</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2164,7 +2260,11 @@
           <t>R5</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2212,7 +2312,11 @@
           <t>R19</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2260,7 +2364,11 @@
           <t>R2</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr"/>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2308,7 +2416,11 @@
           <t>R2</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2356,7 +2468,11 @@
           <t>R2</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2502,7 +2618,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14: the source page /marketing-division-2/ itself now 301s, confirmed via a direct HTTP check; an earlier automated pass misread this because a browser-based crawl follows redirects and reports the destination page instead of the redirect)</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4636,11 @@
           <t>R18</t>
         </is>
       </c>
-      <c r="J84" s="2" t="inlineStr"/>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5048,7 +5168,11 @@
           <t>R18</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr"/>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5384,7 +5508,11 @@
           <t>R18</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr"/>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -5672,7 +5800,11 @@
           <t>R18</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr"/>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -7880,7 +8012,11 @@
           <t>R20</t>
         </is>
       </c>
-      <c r="J154" s="2" t="inlineStr"/>
+      <c r="J154" s="6" t="inlineStr">
+        <is>
+          <t>In progress (verified 2026-09-14: book-a-call now noindexed; lets-talk now redirects to contact-us)</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -8024,7 +8160,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J157" s="2" t="inlineStr"/>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -10282,7 +10422,7 @@
       </c>
       <c r="J204" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10520,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J206" s="2" t="inlineStr"/>
+      <c r="J206" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -10428,7 +10572,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J207" s="2" t="inlineStr"/>
+      <c r="J207" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -10526,7 +10674,7 @@
       </c>
       <c r="J209" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10964,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J215" s="2" t="inlineStr"/>
+      <c r="J215" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -10864,7 +11016,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J216" s="2" t="inlineStr"/>
+      <c r="J216" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -10912,7 +11068,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J217" s="2" t="inlineStr"/>
+      <c r="J217" s="6" t="inlineStr">
+        <is>
+          <t>In progress (verified 2026-09-14: DevNotes from the sheet: "i set it to Non-index", confirmed live: /book-a-call/ now noindex (still 200, not merged into contact-us))</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -10962,7 +11122,7 @@
       </c>
       <c r="J218" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11174,7 @@
       </c>
       <c r="J219" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11066,7 +11226,7 @@
       </c>
       <c r="J220" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11118,7 +11278,7 @@
       </c>
       <c r="J221" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11170,7 +11330,7 @@
       </c>
       <c r="J222" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11222,7 +11382,7 @@
       </c>
       <c r="J223" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11434,7 @@
       </c>
       <c r="J224" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11326,7 +11486,7 @@
       </c>
       <c r="J225" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11538,7 @@
       </c>
       <c r="J226" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11590,7 @@
       </c>
       <c r="J227" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14: 0 em dashes confirmed by a direct fetch of the homepage; the automated crawl that flagged this as reopened hit a screenshot timeout and returned no data for this page, not a real regression)</t>
         </is>
       </c>
     </row>
@@ -11482,7 +11642,7 @@
       </c>
       <c r="J228" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11694,7 @@
       </c>
       <c r="J229" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11746,7 @@
       </c>
       <c r="J230" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11638,7 +11798,7 @@
       </c>
       <c r="J231" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11850,7 @@
       </c>
       <c r="J232" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11742,7 +11902,7 @@
       </c>
       <c r="J233" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11954,7 @@
       </c>
       <c r="J234" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11846,7 +12006,7 @@
       </c>
       <c r="J235" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11898,7 +12058,7 @@
       </c>
       <c r="J236" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -11950,7 +12110,7 @@
       </c>
       <c r="J237" s="6" t="inlineStr">
         <is>
-          <t>In progress (verified 2026-09-11: )</t>
+          <t>In progress (verified 2026-09-14: )</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12162,7 @@
       </c>
       <c r="J238" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -12054,7 +12214,7 @@
       </c>
       <c r="J239" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -12106,7 +12266,7 @@
       </c>
       <c r="J240" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -12158,7 +12318,7 @@
       </c>
       <c r="J241" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-11)</t>
+          <t>Done (verified 2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -12304,7 +12464,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J244" s="2" t="inlineStr"/>
+      <c r="J244" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -12352,7 +12516,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J245" s="2" t="inlineStr"/>
+      <c r="J245" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -12400,7 +12568,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J246" s="2" t="inlineStr"/>
+      <c r="J246" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -12448,7 +12620,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J247" s="2" t="inlineStr"/>
+      <c r="J247" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -12496,7 +12672,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J248" s="2" t="inlineStr"/>
+      <c r="J248" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -12544,7 +12724,11 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J249" s="2" t="inlineStr"/>
+      <c r="J249" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -12592,12 +12776,112 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="J250" s="2" t="inlineStr"/>
+      <c r="J250" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>AS-250</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>New since 2026-09-11</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>About page</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/about-us/</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>Redirected pages were removed without migrating their content first, as the roadmap asked</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>/our-story/, /our-team/, /our-management/, /our-world-wide-team/ and /niftyone-custom-portal/ were all correctly 301-redirected to /about-us/ on or before 2026-09-14 (good, matches the recommended disposition). But the roadmap specifically said to copy the founding story from /our-story/ into /about-us/ before redirecting it. About Us is 648 words today, essentially unchanged from before this batch of redirects (647 words on 2026-09-11), so that migration did not happen: the founding story text itself is gone from the live site, only the URL now forwards visitors to a page that does not contain it.</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>Pull the founding story text from a backup or from a cached copy of /our-story/ and add it to /about-us/ under the existing "Our Story" heading.</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="J251" s="2" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>AS-251</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>New since 2026-09-11</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>About page</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/about-us/</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>New heading has a typo: "Alber Scott Company Summary"</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>A heading reading "Alber Scott Company Summary" (missing the "t" in Albert) now appears on /about-us/, likely added as part of merging in content from one of the five redirected pages.</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>Fix the heading text to "Albert Scott Company Summary".</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J250"/>
+  <autoFilter ref="A1:J252"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J250" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Skipped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12851,6 +13135,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId247"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId248"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId251"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seo-geo/tracking/issue-tracker.xlsx
+++ b/seo-geo/tracking/issue-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Issues" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Issues'!$A$1:$J$252</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Issues'!$A$1:$J$253</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J252"/>
+  <dimension ref="A1:J253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -475,7 +475,7 @@
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -578,7 +578,7 @@
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Open, urgent (confirmed again 2026-09-14: article still not restored, 5 days after it was found deleted)</t>
+          <t>Open, urgent (confirmed again 2026-09-16: article still not restored, 7 days after it was found deleted)</t>
         </is>
       </c>
     </row>
@@ -2416,9 +2416,9 @@
           <t>R2</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>Done (verified 2026-09-14)</t>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>REOPENED (verified 2026-09-16: the homepage still links to https://www.albertscott.com/marketing-division/, which 301s to /marketing-devision/, confirmed by fetching the live homepage HTML directly. Not a measurement error this time; a plain absolute link on the page.)</t>
         </is>
       </c>
     </row>
@@ -2468,9 +2468,9 @@
           <t>R2</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>Done (verified 2026-09-14)</t>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>REOPENED (verified 2026-09-16: the homepage's "Explore Logistics" button in the divisions accordion section links to /logistics-division-2/ (relative href), confirmed by fetching the live homepage HTML directly. A correct absolute link to /logistics-division/ also exists elsewhere on the page, so this looks like a second button using the old URL, not the original one being un-fixed.)</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-14: the source page /marketing-division-2/ itself now 301s, confirmed via a direct HTTP check; an earlier automated pass misread this because a browser-based crawl follows redirects and reports the destination page instead of the redirect)</t>
+          <t>Done (verified 2026-09-16: source page no longer exists as a separate page, moot)</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,11 @@
           <t>R8</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr"/>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -5364,7 +5368,11 @@
           <t>R8</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr"/>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -10472,7 +10480,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J205" s="2" t="inlineStr"/>
+      <c r="J205" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -10624,7 +10636,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J208" s="2" t="inlineStr"/>
+      <c r="J208" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -10724,7 +10740,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J210" s="2" t="inlineStr"/>
+      <c r="J210" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -10772,7 +10792,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J211" s="2" t="inlineStr"/>
+      <c r="J211" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -10820,7 +10844,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J212" s="2" t="inlineStr"/>
+      <c r="J212" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -10868,7 +10896,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J213" s="2" t="inlineStr"/>
+      <c r="J213" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -10916,7 +10948,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J214" s="2" t="inlineStr"/>
+      <c r="J214" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -12110,7 +12146,7 @@
       </c>
       <c r="J237" s="6" t="inlineStr">
         <is>
-          <t>In progress (verified 2026-09-14: )</t>
+          <t>In progress (verified 2026-09-16)</t>
         </is>
       </c>
     </row>
@@ -12876,12 +12912,64 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J252" s="2" t="inlineStr"/>
+      <c r="J252" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>AS-252</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>New since 2026-09-14</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>Homepage</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>A new gallery block on the homepage links every tile to the same redirecting URL</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>Fetching the live homepage HTML on 2026-09-16 shows a gallery grid (class "dsm-gallery", the same Divi Supreme Modules widget behind the dsm-attachment-category taxonomy found on 2026-09-07) with at least 4 tiles, every one linking to /case-studies-2/ (a relative href), which 301s to /case-studies/. This section was not present in earlier checks; it looks like a new homepage block was added using this widget.</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>Point each gallery tile's link directly at https://www.albertscott.com/case-studies/, or at the specific case study each tile represents, instead of the redirecting URL.</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J252"/>
+  <autoFilter ref="A1:J253"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J253" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Done,Skipped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13137,6 +13225,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId249"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId252"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seo-geo/tracking/issue-tracker.xlsx
+++ b/seo-geo/tracking/issue-tracker.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Open, urgent (confirmed again 2026-09-16: article still not restored, 7 days after it was found deleted)</t>
+          <t>Open, urgent (confirmed again 2026-09-17: article still not restored, 8 days since it was found deleted, and per Hassan's 2026-09-16 reply the deletion was intentional, not accidental -- see the audit note)</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-14)</t>
+          <t>Done (verified 2026-09-17: now returns a 301 redirect to the homepage, an upgrade from the noindex it had before)</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-14)</t>
+          <t>Done (verified 2026-09-17: now returns a 301 redirect to the homepage, an upgrade from the noindex it had before)</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-14)</t>
+          <t>Done (verified 2026-09-17: now returns a 301 redirect to the homepage, an upgrade from the noindex it had before)</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-14)</t>
+          <t>Done (verified 2026-09-17: now returns a 301 redirect to the homepage, an upgrade from the noindex it had before)</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Done (verified 2026-09-16: source page no longer exists as a separate page, moot)</t>
+          <t>Done (verified 2026-09-17: source page no longer exists as a separate page, moot)</t>
         </is>
       </c>
     </row>

--- a/seo-geo/tracking/issue-tracker.xlsx
+++ b/seo-geo/tracking/issue-tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Issues" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Issues'!$A$1:$J$253</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Issues'!$A$1:$J$254</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,19 +463,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J253"/>
+  <dimension ref="A1:J254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="80" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -628,7 +628,11 @@
           <t>R15</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-18: both Organization nodes now share @id https://www.albertscott.com/#organization, confirmed by fetching and parsing both JSON-LD blocks directly. numberOfEmployees is also now unified at 30 in both, which was not explicitly claimed but is also fixed.)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -676,7 +680,11 @@
           <t>R15</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-18: sameAs now present with LinkedIn and Crunchbase URLs, confirmed directly in the live JSON-LD.)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -772,7 +780,11 @@
           <t>G1</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>OPEN, not fixed (checked 2026-09-18: the AIOSEO schema block still declares description "E-commerce Management", unchanged, still conflicting with the homepage meta description. Do not conflate this with AS-001/AS-002 being fixed, they are related but this specific one is not done.)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2416,9 +2428,9 @@
           <t>R2</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>REOPENED (verified 2026-09-16: the homepage still links to https://www.albertscott.com/marketing-division/, which 301s to /marketing-devision/, confirmed by fetching the live homepage HTML directly. Not a measurement error this time; a plain absolute link on the page.)</t>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>RESOLVED, stale finding (checked 2026-09-18: /marketing-division/ is now the live, correct-spelling canonical page (200, real content, confirmed by title and H1), and the old misspelled /marketing-devision/ now 301s to it. The homepage linking to /marketing-division/ is now correct, not a bug. This tracker had the direction backwards; corrected.)</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2482,7 @@
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>REOPENED (verified 2026-09-16: the homepage's "Explore Logistics" button in the divisions accordion section links to /logistics-division-2/ (relative href), confirmed by fetching the live homepage HTML directly. A correct absolute link to /logistics-division/ also exists elsewhere on the page, so this looks like a second button using the old URL, not the original one being un-fixed.)</t>
+          <t>REOPENED (confirmed again 2026-09-18: the "Explore Logistics" button still links to /logistics-division-2/, which still 301s. This one is still a real, open problem, unlike AS-036.)</t>
         </is>
       </c>
     </row>
@@ -12966,13 +12978,56 @@
       </c>
       <c r="J253" s="2" t="inlineStr"/>
     </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>AS-253</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>New since 2026-09-17</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>Legacy services page</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>https://www.albertscott.com/services/</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>A live pricing figure (9% commission) is exposed inside broken shortcode text on an indexable page</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>Fetching /services/ directly on 2026-09-18 shows raw, unrendered Visual Composer shortcode text on screen and in the meta description, exactly as flagged elsewhere (AS-197). Within that shortcode text, the literal strings "9% Commission" and "9% Service" appear, a real pricing figure, visible to any visitor and any crawler. The same shortcode-broken pattern is confirmed still live on /our-service/ (AS-199), /overview/ (AS-201), and /additional-services/ (AS-200) as well; none contain a comparable pricing figure on inspection today. This is the same set of pages Hassan gave as his justification for deleting AS-000 (shortcode-broken content), which is still live and unaddressed while AS-000 was removed.</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>Treat this with more urgency than the general legacy-page cleanup: confirm with Yoni whether this pricing figure is current or stale before doing anything else, then redirect or rebuild the page per the existing AS-197 recommendation.</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J253"/>
-  <dataValidations count="1">
-    <dataValidation sqref="J2:J253" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Open,In progress,Done,Skipped"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:J254"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -13226,6 +13281,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId251"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId253"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/seo-geo/tracking/issue-tracker.xlsx
+++ b/seo-geo/tracking/issue-tracker.xlsx
@@ -3640,7 +3640,11 @@
           <t>R3</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr"/>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: live title tag now reads "Marketing division - Albert Scott" (correct spelling) and the AIOSEO breadcrumb schema no longer says "Devision". https://www.albertscott.com/marketing-division/ is now the canonical 200 page; https://www.albertscott.com/marketing-devision/ 301s to it. Note: one sitewide nav menu link still points at the old /marketing-devision/ URL, which still works via the redirect but adds an unnecessary hop; minor, not blocking this row.)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -8808,7 +8812,11 @@
           <t>R13</t>
         </is>
       </c>
-      <c r="J170" s="2" t="inlineStr"/>
+      <c r="J170" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/project/national-public-seatinf/ now 301s to the corrected slug https://www.albertscott.com/project/national-public-seating/.)</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -9432,7 +9440,11 @@
           <t>R13</t>
         </is>
       </c>
-      <c r="J183" s="2" t="inlineStr"/>
+      <c r="J183" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: same fix as AS-168, confirmed by direct request, 301 to the corrected slug.)</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -9480,7 +9492,11 @@
           <t>R12</t>
         </is>
       </c>
-      <c r="J184" s="2" t="inlineStr"/>
+      <c r="J184" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/blog/mouthwatchers/ now 301s to https://www.albertscott.com/case-studies/mouthwatchers/, exactly the recommended fix.)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -9864,7 +9880,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J192" s="2" t="inlineStr"/>
+      <c r="J192" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/home/ now 301s to https://www.albertscott.com/.)</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -9912,7 +9932,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J193" s="2" t="inlineStr"/>
+      <c r="J193" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/amazon-management-agency/ now 301s to https://www.albertscott.com/.)</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -9960,7 +9984,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J194" s="2" t="inlineStr"/>
+      <c r="J194" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/for-amazon-brands/ now carries meta robots "noindex, nofollow...". Page still returns 200 but is out of the index, matching the recommended fix for an active ad landing page.)</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -10008,7 +10036,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J195" s="2" t="inlineStr"/>
+      <c r="J195" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/for-amazon-brandsv2/ now carries the same noindex robots tag.)</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -10056,7 +10088,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J196" s="2" t="inlineStr"/>
+      <c r="J196" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/amazon-growth-audit/ now carries the same noindex robots tag.)</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -10104,7 +10140,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J197" s="2" t="inlineStr"/>
+      <c r="J197" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/amazon-growth-audit-v2/ now returns 404, functionally the same outcome as the recommended delete/410.)</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -10152,7 +10192,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J198" s="2" t="inlineStr"/>
+      <c r="J198" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/form-ads-test/ now returns 404.)</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -10200,7 +10244,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J199" s="2" t="inlineStr"/>
+      <c r="J199" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/services/ now 301s to https://www.albertscott.com/. This also resolves AS-253, the pricing figure that was exposed in this page's broken shortcode text; that content is no longer served.)</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -10248,7 +10296,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J200" s="2" t="inlineStr"/>
+      <c r="J200" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/services-2/ now 301s to https://www.albertscott.com/.)</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -10296,7 +10348,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J201" s="2" t="inlineStr"/>
+      <c r="J201" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/our-service/ now 301s to https://www.albertscott.com/.)</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -10344,7 +10400,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J202" s="2" t="inlineStr"/>
+      <c r="J202" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/additional-services/ now 301s to https://www.albertscott.com/.)</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -10392,7 +10452,11 @@
           <t>R1</t>
         </is>
       </c>
-      <c r="J203" s="2" t="inlineStr"/>
+      <c r="J203" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: https://www.albertscott.com/overview/ now 301s to https://www.albertscott.com/.)</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -12876,7 +12940,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J251" s="2" t="inlineStr"/>
+      <c r="J251" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: /about-us/ now has a "Our Story" section reading "Albert Scott was founded in 2020 by David Greenblatt and Shlomo Greenblatt after seeing firsthand how difficult it had become for brands to succeed on Amazon...". The founding story is present, and the page grew from 648 to 721 words to hold it.)</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -13024,7 +13092,11 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J254" s="2" t="inlineStr"/>
+      <c r="J254" s="5" t="inlineStr">
+        <is>
+          <t>Done (verified 2026-09-21: /services/ now 301s to the homepage instead of serving the broken shortcode page, so the "9% Commission" pricing text is no longer exposed. Resolved as a side effect of the AS-197 redirect.)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J254"/>
